--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815684</v>
+        <v>119815382</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>97928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459038</v>
+        <v>459422</v>
       </c>
       <c r="R2" t="n">
-        <v>7072466</v>
+        <v>7072241</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815752</v>
+        <v>119815623</v>
       </c>
       <c r="B3" t="n">
-        <v>86878</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459039</v>
+        <v>459346</v>
       </c>
       <c r="R3" t="n">
-        <v>7072515</v>
+        <v>7072280</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815382</v>
+        <v>119815752</v>
       </c>
       <c r="B4" t="n">
-        <v>97928</v>
+        <v>86878</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459422</v>
+        <v>459039</v>
       </c>
       <c r="R4" t="n">
-        <v>7072241</v>
+        <v>7072515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815753</v>
+        <v>119815684</v>
       </c>
       <c r="B5" t="n">
-        <v>86878</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459015</v>
+        <v>459038</v>
       </c>
       <c r="R5" t="n">
-        <v>7072472</v>
+        <v>7072466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815650</v>
+        <v>119815629</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459053</v>
+        <v>459115</v>
       </c>
       <c r="R6" t="n">
-        <v>7072479</v>
+        <v>7072438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815617</v>
+        <v>119815293</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459282</v>
+        <v>459013</v>
       </c>
       <c r="R7" t="n">
-        <v>7072334</v>
+        <v>7072470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815623</v>
+        <v>119815617</v>
       </c>
       <c r="B8" t="n">
         <v>90580</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459346</v>
+        <v>459282</v>
       </c>
       <c r="R8" t="n">
-        <v>7072280</v>
+        <v>7072334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815629</v>
+        <v>119815753</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459115</v>
+        <v>459015</v>
       </c>
       <c r="R9" t="n">
-        <v>7072438</v>
+        <v>7072472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815293</v>
+        <v>119815650</v>
       </c>
       <c r="B10" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459013</v>
+        <v>459053</v>
       </c>
       <c r="R10" t="n">
-        <v>7072470</v>
+        <v>7072479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815623</v>
+        <v>119815684</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459346</v>
+        <v>459038</v>
       </c>
       <c r="R3" t="n">
-        <v>7072280</v>
+        <v>7072466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815752</v>
+        <v>119815753</v>
       </c>
       <c r="B4" t="n">
         <v>86878</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459039</v>
+        <v>459015</v>
       </c>
       <c r="R4" t="n">
-        <v>7072515</v>
+        <v>7072472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815684</v>
+        <v>119815623</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459038</v>
+        <v>459346</v>
       </c>
       <c r="R5" t="n">
-        <v>7072466</v>
+        <v>7072280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815629</v>
+        <v>119815752</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459115</v>
+        <v>459039</v>
       </c>
       <c r="R6" t="n">
-        <v>7072438</v>
+        <v>7072515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815293</v>
+        <v>119815617</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459013</v>
+        <v>459282</v>
       </c>
       <c r="R7" t="n">
-        <v>7072470</v>
+        <v>7072334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815617</v>
+        <v>119815650</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459282</v>
+        <v>459053</v>
       </c>
       <c r="R8" t="n">
-        <v>7072334</v>
+        <v>7072479</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815753</v>
+        <v>119815629</v>
       </c>
       <c r="B9" t="n">
-        <v>86878</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459015</v>
+        <v>459115</v>
       </c>
       <c r="R9" t="n">
-        <v>7072472</v>
+        <v>7072438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815650</v>
+        <v>119815606</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459053</v>
+        <v>458998</v>
       </c>
       <c r="R10" t="n">
-        <v>7072479</v>
+        <v>7072440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815606</v>
+        <v>119815293</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>91254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458998</v>
+        <v>459013</v>
       </c>
       <c r="R11" t="n">
-        <v>7072440</v>
+        <v>7072470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815382</v>
+        <v>119815753</v>
       </c>
       <c r="B2" t="n">
-        <v>97928</v>
+        <v>86878</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459422</v>
+        <v>459015</v>
       </c>
       <c r="R2" t="n">
-        <v>7072241</v>
+        <v>7072472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815753</v>
+        <v>119815382</v>
       </c>
       <c r="B4" t="n">
-        <v>86878</v>
+        <v>97928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459015</v>
+        <v>459422</v>
       </c>
       <c r="R4" t="n">
-        <v>7072472</v>
+        <v>7072241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815753</v>
+        <v>119815684</v>
       </c>
       <c r="B2" t="n">
-        <v>86878</v>
+        <v>82305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459015</v>
+        <v>459038</v>
       </c>
       <c r="R2" t="n">
-        <v>7072472</v>
+        <v>7072466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815684</v>
+        <v>119815650</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459038</v>
+        <v>459053</v>
       </c>
       <c r="R3" t="n">
-        <v>7072466</v>
+        <v>7072479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815382</v>
+        <v>119815629</v>
       </c>
       <c r="B4" t="n">
-        <v>97928</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459422</v>
+        <v>459115</v>
       </c>
       <c r="R4" t="n">
-        <v>7072241</v>
+        <v>7072438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815752</v>
+        <v>119815606</v>
       </c>
       <c r="B6" t="n">
-        <v>86878</v>
+        <v>90576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459039</v>
+        <v>458998</v>
       </c>
       <c r="R6" t="n">
-        <v>7072515</v>
+        <v>7072440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815617</v>
+        <v>119815752</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459282</v>
+        <v>459039</v>
       </c>
       <c r="R7" t="n">
-        <v>7072334</v>
+        <v>7072515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815650</v>
+        <v>119815617</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459053</v>
+        <v>459282</v>
       </c>
       <c r="R8" t="n">
-        <v>7072479</v>
+        <v>7072334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815629</v>
+        <v>119815753</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459115</v>
+        <v>459015</v>
       </c>
       <c r="R9" t="n">
-        <v>7072438</v>
+        <v>7072472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815606</v>
+        <v>119815293</v>
       </c>
       <c r="B10" t="n">
-        <v>90576</v>
+        <v>91254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458998</v>
+        <v>459013</v>
       </c>
       <c r="R10" t="n">
-        <v>7072440</v>
+        <v>7072470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815293</v>
+        <v>119815382</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>97928</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459013</v>
+        <v>459422</v>
       </c>
       <c r="R11" t="n">
-        <v>7072470</v>
+        <v>7072241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815684</v>
+        <v>119815629</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459038</v>
+        <v>459115</v>
       </c>
       <c r="R2" t="n">
-        <v>7072466</v>
+        <v>7072438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815650</v>
+        <v>119815623</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459053</v>
+        <v>459346</v>
       </c>
       <c r="R3" t="n">
-        <v>7072479</v>
+        <v>7072280</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815629</v>
+        <v>119815650</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459115</v>
+        <v>459053</v>
       </c>
       <c r="R4" t="n">
-        <v>7072438</v>
+        <v>7072479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815623</v>
+        <v>119815293</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>91272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459346</v>
+        <v>459013</v>
       </c>
       <c r="R5" t="n">
-        <v>7072280</v>
+        <v>7072470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815606</v>
+        <v>119815752</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>86895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458998</v>
+        <v>459039</v>
       </c>
       <c r="R6" t="n">
-        <v>7072440</v>
+        <v>7072515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815752</v>
+        <v>119815753</v>
       </c>
       <c r="B7" t="n">
-        <v>86878</v>
+        <v>86895</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459039</v>
+        <v>459015</v>
       </c>
       <c r="R7" t="n">
-        <v>7072515</v>
+        <v>7072472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>119815617</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815753</v>
+        <v>119815606</v>
       </c>
       <c r="B9" t="n">
-        <v>86878</v>
+        <v>90594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459015</v>
+        <v>458998</v>
       </c>
       <c r="R9" t="n">
-        <v>7072472</v>
+        <v>7072440</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815293</v>
+        <v>119815382</v>
       </c>
       <c r="B10" t="n">
-        <v>91254</v>
+        <v>97951</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459013</v>
+        <v>459422</v>
       </c>
       <c r="R10" t="n">
-        <v>7072470</v>
+        <v>7072241</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815382</v>
+        <v>119815684</v>
       </c>
       <c r="B11" t="n">
-        <v>97928</v>
+        <v>82321</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459422</v>
+        <v>459038</v>
       </c>
       <c r="R11" t="n">
-        <v>7072241</v>
+        <v>7072466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815606</v>
+        <v>119815382</v>
       </c>
       <c r="B9" t="n">
-        <v>90594</v>
+        <v>97951</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458998</v>
+        <v>459422</v>
       </c>
       <c r="R9" t="n">
-        <v>7072440</v>
+        <v>7072241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815382</v>
+        <v>119815606</v>
       </c>
       <c r="B10" t="n">
-        <v>97951</v>
+        <v>90594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459422</v>
+        <v>458998</v>
       </c>
       <c r="R10" t="n">
-        <v>7072241</v>
+        <v>7072440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815629</v>
+        <v>119815753</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>86895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459115</v>
+        <v>459015</v>
       </c>
       <c r="R2" t="n">
-        <v>7072438</v>
+        <v>7072472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815623</v>
+        <v>119815684</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459346</v>
+        <v>459038</v>
       </c>
       <c r="R3" t="n">
-        <v>7072280</v>
+        <v>7072466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815650</v>
+        <v>119815617</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459053</v>
+        <v>459282</v>
       </c>
       <c r="R4" t="n">
-        <v>7072479</v>
+        <v>7072334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815293</v>
+        <v>119815629</v>
       </c>
       <c r="B5" t="n">
-        <v>91272</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459013</v>
+        <v>459115</v>
       </c>
       <c r="R5" t="n">
-        <v>7072470</v>
+        <v>7072438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815752</v>
+        <v>119815623</v>
       </c>
       <c r="B6" t="n">
-        <v>86895</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459039</v>
+        <v>459346</v>
       </c>
       <c r="R6" t="n">
-        <v>7072515</v>
+        <v>7072280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815753</v>
+        <v>119815752</v>
       </c>
       <c r="B7" t="n">
         <v>86895</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459015</v>
+        <v>459039</v>
       </c>
       <c r="R7" t="n">
-        <v>7072472</v>
+        <v>7072515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815617</v>
+        <v>119815606</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459282</v>
+        <v>458998</v>
       </c>
       <c r="R8" t="n">
-        <v>7072334</v>
+        <v>7072440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815382</v>
+        <v>119815650</v>
       </c>
       <c r="B9" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459422</v>
+        <v>459053</v>
       </c>
       <c r="R9" t="n">
-        <v>7072241</v>
+        <v>7072479</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815606</v>
+        <v>119815293</v>
       </c>
       <c r="B10" t="n">
-        <v>90594</v>
+        <v>91272</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458998</v>
+        <v>459013</v>
       </c>
       <c r="R10" t="n">
-        <v>7072440</v>
+        <v>7072470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119815684</v>
+        <v>119815382</v>
       </c>
       <c r="B11" t="n">
-        <v>82321</v>
+        <v>97951</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459038</v>
+        <v>459422</v>
       </c>
       <c r="R11" t="n">
-        <v>7072466</v>
+        <v>7072241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119815753</v>
+        <v>119815650</v>
       </c>
       <c r="B2" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459015</v>
+        <v>459053</v>
       </c>
       <c r="R2" t="n">
-        <v>7072472</v>
+        <v>7072479</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119815684</v>
+        <v>119815752</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>86895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459038</v>
+        <v>459039</v>
       </c>
       <c r="R3" t="n">
-        <v>7072466</v>
+        <v>7072515</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119815617</v>
+        <v>119815629</v>
       </c>
       <c r="B4" t="n">
         <v>90598</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459282</v>
+        <v>459115</v>
       </c>
       <c r="R4" t="n">
-        <v>7072334</v>
+        <v>7072438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119815629</v>
+        <v>119815623</v>
       </c>
       <c r="B5" t="n">
         <v>90598</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459115</v>
+        <v>459346</v>
       </c>
       <c r="R5" t="n">
-        <v>7072438</v>
+        <v>7072280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119815623</v>
+        <v>119815606</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459346</v>
+        <v>458998</v>
       </c>
       <c r="R6" t="n">
-        <v>7072280</v>
+        <v>7072440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119815752</v>
+        <v>119815293</v>
       </c>
       <c r="B7" t="n">
-        <v>86895</v>
+        <v>91272</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459039</v>
+        <v>459013</v>
       </c>
       <c r="R7" t="n">
-        <v>7072515</v>
+        <v>7072470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119815606</v>
+        <v>119815753</v>
       </c>
       <c r="B8" t="n">
-        <v>90594</v>
+        <v>86895</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458998</v>
+        <v>459015</v>
       </c>
       <c r="R8" t="n">
-        <v>7072440</v>
+        <v>7072472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119815650</v>
+        <v>119815684</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459053</v>
+        <v>459038</v>
       </c>
       <c r="R9" t="n">
-        <v>7072479</v>
+        <v>7072466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119815293</v>
+        <v>119815617</v>
       </c>
       <c r="B10" t="n">
-        <v>91272</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459013</v>
+        <v>459282</v>
       </c>
       <c r="R10" t="n">
-        <v>7072470</v>
+        <v>7072334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 12809-2024 artfynd.xlsx
+++ b/artfynd/A 12809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY164"/>
+  <dimension ref="A1:AZ164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815233</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815752</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815604</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815683</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815293</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815650</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815655</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815661</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815709</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815382</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815386</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119815232</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487060</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490676</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490751</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2672,6 +2772,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502981</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490708</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2867,6 +2977,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490756</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2964,6 +3079,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502982</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3061,6 +3181,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487046</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3158,6 +3283,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487047</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3255,6 +3385,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490462</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3352,6 +3487,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490691</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3449,6 +3589,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490692</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3546,6 +3691,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490693</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3643,6 +3793,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490694</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3740,6 +3895,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490695</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3837,6 +3997,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87491173</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3934,6 +4099,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502970</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4031,6 +4201,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490677</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4128,6 +4303,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490673</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4225,6 +4405,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490674</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4322,6 +4507,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490675</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4419,6 +4609,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502963</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4516,6 +4711,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490754</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4613,6 +4813,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490755</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4710,6 +4915,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4807,6 +5017,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490671</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4904,6 +5119,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490696</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5001,6 +5221,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490697</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5098,6 +5323,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490698</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5195,6 +5425,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490699</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5292,6 +5527,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490701</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5389,6 +5629,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5486,6 +5731,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5583,6 +5833,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487050</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5680,6 +5935,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487051</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5777,6 +6037,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487052</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5874,6 +6139,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5971,6 +6241,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6068,6 +6343,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6165,6 +6445,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490465</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6262,6 +6547,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490466</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6359,6 +6649,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490467</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6456,6 +6751,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490469</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6553,6 +6853,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490470</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6650,6 +6955,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490471</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6747,6 +7057,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490713</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6844,6 +7159,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490714</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6941,6 +7261,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490715</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7038,6 +7363,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490716</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7135,6 +7465,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490717</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7232,6 +7567,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490718</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7329,6 +7669,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490719</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7426,6 +7771,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490720</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7523,6 +7873,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502966</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7620,6 +7975,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502973</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7717,6 +8077,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502974</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7814,6 +8179,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487042</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7911,6 +8281,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487043</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8008,6 +8383,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487044</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8105,6 +8485,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487045</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8202,6 +8587,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490452</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8299,6 +8689,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490454</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8396,6 +8791,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490455</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8493,6 +8893,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490456</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8590,6 +8995,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490457</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8687,6 +9097,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490458</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8784,6 +9199,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490459</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8881,6 +9301,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490460</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8978,6 +9403,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490461</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9075,6 +9505,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490684</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9172,6 +9607,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490685</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9269,6 +9709,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490686</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9366,6 +9811,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490687</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9463,6 +9913,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87491172</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9560,6 +10015,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87491175</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9657,6 +10117,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502967</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9754,6 +10219,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502983</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9851,6 +10321,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487061</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9948,6 +10423,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487062</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10045,6 +10525,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490479</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10142,6 +10627,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490480</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10239,6 +10729,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490482</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10336,6 +10831,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490483</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10433,6 +10933,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490762</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10530,6 +11035,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490763</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10627,6 +11137,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490764</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10724,6 +11239,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490765</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10821,6 +11341,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490766</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10918,6 +11443,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490767</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11015,6 +11545,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490768</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11112,6 +11647,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87491180</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11209,6 +11749,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87491189</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11306,6 +11851,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502984</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11403,6 +11953,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487056</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11500,6 +12055,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487057</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11597,6 +12157,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490472</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11694,6 +12259,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490473</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11791,6 +12361,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490474</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11888,6 +12463,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490722</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11985,6 +12565,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490723</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12082,6 +12667,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490724</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12179,6 +12769,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490725</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12276,6 +12871,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490726</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12373,6 +12973,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490727</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12470,6 +13075,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490728</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12567,6 +13177,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490729</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12664,6 +13279,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87491181</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12761,6 +13381,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502972</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12858,6 +13483,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502976</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12955,6 +13585,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490682</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13052,6 +13687,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502964</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13149,6 +13789,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487059</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13246,6 +13891,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490731</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13343,6 +13993,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490732</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13440,6 +14095,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490733</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13537,6 +14197,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490736</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13634,6 +14299,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487058</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13731,6 +14401,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490451</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13828,6 +14503,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490666</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13925,6 +14605,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490668</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14022,6 +14707,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490704</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14119,6 +14809,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490689</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14216,6 +14911,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490681</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14313,6 +15013,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490759</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14410,6 +15115,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490760</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14507,6 +15217,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87487041</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14604,6 +15319,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490683</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14701,6 +15421,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502980</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14799,6 +15524,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490669</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14897,6 +15627,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490678</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14995,6 +15730,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490679</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15088,6 +15828,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490476</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15185,6 +15930,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490475</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15282,6 +16032,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490737</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15379,6 +16134,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490738</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15476,6 +16236,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490739</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15573,6 +16338,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490740</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15670,6 +16440,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502971</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15767,6 +16542,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502975</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15864,6 +16644,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502977</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15961,6 +16746,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502979</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16072,6 +16862,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89715062</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16183,6 +16978,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89715080</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16280,6 +17080,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490748</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16377,6 +17182,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490749</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16474,6 +17284,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490750</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16571,8 +17386,178 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>